--- a/UNLID_財務モデル_v4.2.xlsx
+++ b/UNLID_財務モデル_v4.2.xlsx
@@ -13,6 +13,7 @@
     <sheet name="BS（貸借対照表）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="月次CF（36ヶ月）" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="感度分析" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SME単価市場調査" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68,7 +69,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -130,8 +131,38 @@
         <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,11 +176,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -274,6 +333,47 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2681,10 +2781,10 @@
           <t>▌売上高</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2784,10 +2884,10 @@
           <t>▌売上原価（COGS）</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
+      <c r="B10" s="43" t="n"/>
+      <c r="C10" s="43" t="n"/>
+      <c r="D10" s="43" t="n"/>
+      <c r="E10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2930,10 +3030,10 @@
           <t>▌SG&amp;A（販売費及び一般管理費）</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="22" t="n"/>
+      <c r="B17" s="43" t="n"/>
+      <c r="C17" s="43" t="n"/>
+      <c r="D17" s="43" t="n"/>
+      <c r="E17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -3283,10 +3383,10 @@
           <t>▌参考指標</t>
         </is>
       </c>
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="43" t="n"/>
+      <c r="E33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="26" t="inlineStr">
@@ -3410,10 +3510,10 @@
           <t>▌流動資産</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3489,10 +3589,10 @@
           <t>▌固定資産</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+      <c r="E9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -3568,10 +3668,10 @@
           <t>▌流動負債</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="E14" s="44" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -3646,10 +3746,10 @@
           <t>▌固定負債</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
+      <c r="B18" s="43" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="44" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -3726,10 +3826,10 @@
           <t>▌純資産</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
+      <c r="B23" s="43" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
+      <c r="E23" s="44" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3847,12 +3947,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A23:E23"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4132,42 +4232,42 @@
           <t>▌売上高</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="22" t="n"/>
-      <c r="I5" s="22" t="n"/>
-      <c r="J5" s="22" t="n"/>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="22" t="n"/>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="22" t="n"/>
-      <c r="P5" s="22" t="n"/>
-      <c r="Q5" s="22" t="n"/>
-      <c r="R5" s="22" t="n"/>
-      <c r="S5" s="22" t="n"/>
-      <c r="T5" s="22" t="n"/>
-      <c r="U5" s="22" t="n"/>
-      <c r="V5" s="22" t="n"/>
-      <c r="W5" s="22" t="n"/>
-      <c r="X5" s="22" t="n"/>
-      <c r="Y5" s="22" t="n"/>
-      <c r="Z5" s="22" t="n"/>
-      <c r="AA5" s="22" t="n"/>
-      <c r="AB5" s="22" t="n"/>
-      <c r="AC5" s="22" t="n"/>
-      <c r="AD5" s="22" t="n"/>
-      <c r="AE5" s="22" t="n"/>
-      <c r="AF5" s="22" t="n"/>
-      <c r="AG5" s="22" t="n"/>
-      <c r="AH5" s="22" t="n"/>
-      <c r="AI5" s="22" t="n"/>
-      <c r="AJ5" s="22" t="n"/>
-      <c r="AK5" s="22" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="43" t="n"/>
+      <c r="H5" s="43" t="n"/>
+      <c r="I5" s="43" t="n"/>
+      <c r="J5" s="43" t="n"/>
+      <c r="K5" s="43" t="n"/>
+      <c r="L5" s="43" t="n"/>
+      <c r="M5" s="43" t="n"/>
+      <c r="N5" s="43" t="n"/>
+      <c r="O5" s="43" t="n"/>
+      <c r="P5" s="43" t="n"/>
+      <c r="Q5" s="43" t="n"/>
+      <c r="R5" s="43" t="n"/>
+      <c r="S5" s="43" t="n"/>
+      <c r="T5" s="43" t="n"/>
+      <c r="U5" s="43" t="n"/>
+      <c r="V5" s="43" t="n"/>
+      <c r="W5" s="43" t="n"/>
+      <c r="X5" s="43" t="n"/>
+      <c r="Y5" s="43" t="n"/>
+      <c r="Z5" s="43" t="n"/>
+      <c r="AA5" s="43" t="n"/>
+      <c r="AB5" s="43" t="n"/>
+      <c r="AC5" s="43" t="n"/>
+      <c r="AD5" s="43" t="n"/>
+      <c r="AE5" s="43" t="n"/>
+      <c r="AF5" s="43" t="n"/>
+      <c r="AG5" s="43" t="n"/>
+      <c r="AH5" s="43" t="n"/>
+      <c r="AI5" s="43" t="n"/>
+      <c r="AJ5" s="43" t="n"/>
+      <c r="AK5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4779,42 +4879,42 @@
           <t>▌売上原価・粗利</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="22" t="n"/>
-      <c r="R10" s="22" t="n"/>
-      <c r="S10" s="22" t="n"/>
-      <c r="T10" s="22" t="n"/>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="22" t="n"/>
-      <c r="W10" s="22" t="n"/>
-      <c r="X10" s="22" t="n"/>
-      <c r="Y10" s="22" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="22" t="n"/>
-      <c r="AB10" s="22" t="n"/>
-      <c r="AC10" s="22" t="n"/>
-      <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="22" t="n"/>
-      <c r="AF10" s="22" t="n"/>
-      <c r="AG10" s="22" t="n"/>
-      <c r="AH10" s="22" t="n"/>
-      <c r="AI10" s="22" t="n"/>
-      <c r="AJ10" s="22" t="n"/>
-      <c r="AK10" s="22" t="n"/>
+      <c r="B10" s="43" t="n"/>
+      <c r="C10" s="43" t="n"/>
+      <c r="D10" s="43" t="n"/>
+      <c r="E10" s="43" t="n"/>
+      <c r="F10" s="43" t="n"/>
+      <c r="G10" s="43" t="n"/>
+      <c r="H10" s="43" t="n"/>
+      <c r="I10" s="43" t="n"/>
+      <c r="J10" s="43" t="n"/>
+      <c r="K10" s="43" t="n"/>
+      <c r="L10" s="43" t="n"/>
+      <c r="M10" s="43" t="n"/>
+      <c r="N10" s="43" t="n"/>
+      <c r="O10" s="43" t="n"/>
+      <c r="P10" s="43" t="n"/>
+      <c r="Q10" s="43" t="n"/>
+      <c r="R10" s="43" t="n"/>
+      <c r="S10" s="43" t="n"/>
+      <c r="T10" s="43" t="n"/>
+      <c r="U10" s="43" t="n"/>
+      <c r="V10" s="43" t="n"/>
+      <c r="W10" s="43" t="n"/>
+      <c r="X10" s="43" t="n"/>
+      <c r="Y10" s="43" t="n"/>
+      <c r="Z10" s="43" t="n"/>
+      <c r="AA10" s="43" t="n"/>
+      <c r="AB10" s="43" t="n"/>
+      <c r="AC10" s="43" t="n"/>
+      <c r="AD10" s="43" t="n"/>
+      <c r="AE10" s="43" t="n"/>
+      <c r="AF10" s="43" t="n"/>
+      <c r="AG10" s="43" t="n"/>
+      <c r="AH10" s="43" t="n"/>
+      <c r="AI10" s="43" t="n"/>
+      <c r="AJ10" s="43" t="n"/>
+      <c r="AK10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="34" t="inlineStr">
@@ -5124,42 +5224,42 @@
           <t>▌SG&amp;A・営業利益</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="22" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="22" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
-      <c r="J13" s="22" t="n"/>
-      <c r="K13" s="22" t="n"/>
-      <c r="L13" s="22" t="n"/>
-      <c r="M13" s="22" t="n"/>
-      <c r="N13" s="22" t="n"/>
-      <c r="O13" s="22" t="n"/>
-      <c r="P13" s="22" t="n"/>
-      <c r="Q13" s="22" t="n"/>
-      <c r="R13" s="22" t="n"/>
-      <c r="S13" s="22" t="n"/>
-      <c r="T13" s="22" t="n"/>
-      <c r="U13" s="22" t="n"/>
-      <c r="V13" s="22" t="n"/>
-      <c r="W13" s="22" t="n"/>
-      <c r="X13" s="22" t="n"/>
-      <c r="Y13" s="22" t="n"/>
-      <c r="Z13" s="22" t="n"/>
-      <c r="AA13" s="22" t="n"/>
-      <c r="AB13" s="22" t="n"/>
-      <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="22" t="n"/>
-      <c r="AE13" s="22" t="n"/>
-      <c r="AF13" s="22" t="n"/>
-      <c r="AG13" s="22" t="n"/>
-      <c r="AH13" s="22" t="n"/>
-      <c r="AI13" s="22" t="n"/>
-      <c r="AJ13" s="22" t="n"/>
-      <c r="AK13" s="22" t="n"/>
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="E13" s="43" t="n"/>
+      <c r="F13" s="43" t="n"/>
+      <c r="G13" s="43" t="n"/>
+      <c r="H13" s="43" t="n"/>
+      <c r="I13" s="43" t="n"/>
+      <c r="J13" s="43" t="n"/>
+      <c r="K13" s="43" t="n"/>
+      <c r="L13" s="43" t="n"/>
+      <c r="M13" s="43" t="n"/>
+      <c r="N13" s="43" t="n"/>
+      <c r="O13" s="43" t="n"/>
+      <c r="P13" s="43" t="n"/>
+      <c r="Q13" s="43" t="n"/>
+      <c r="R13" s="43" t="n"/>
+      <c r="S13" s="43" t="n"/>
+      <c r="T13" s="43" t="n"/>
+      <c r="U13" s="43" t="n"/>
+      <c r="V13" s="43" t="n"/>
+      <c r="W13" s="43" t="n"/>
+      <c r="X13" s="43" t="n"/>
+      <c r="Y13" s="43" t="n"/>
+      <c r="Z13" s="43" t="n"/>
+      <c r="AA13" s="43" t="n"/>
+      <c r="AB13" s="43" t="n"/>
+      <c r="AC13" s="43" t="n"/>
+      <c r="AD13" s="43" t="n"/>
+      <c r="AE13" s="43" t="n"/>
+      <c r="AF13" s="43" t="n"/>
+      <c r="AG13" s="43" t="n"/>
+      <c r="AH13" s="43" t="n"/>
+      <c r="AI13" s="43" t="n"/>
+      <c r="AJ13" s="43" t="n"/>
+      <c r="AK13" s="44" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="34" t="inlineStr">
@@ -5810,42 +5910,42 @@
           <t>▌月次キャッシュフロー</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="22" t="n"/>
-      <c r="W19" s="22" t="n"/>
-      <c r="X19" s="22" t="n"/>
-      <c r="Y19" s="22" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="22" t="n"/>
-      <c r="AB19" s="22" t="n"/>
-      <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="22" t="n"/>
-      <c r="AF19" s="22" t="n"/>
-      <c r="AG19" s="22" t="n"/>
-      <c r="AH19" s="22" t="n"/>
-      <c r="AI19" s="22" t="n"/>
-      <c r="AJ19" s="22" t="n"/>
-      <c r="AK19" s="22" t="n"/>
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="43" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="E19" s="43" t="n"/>
+      <c r="F19" s="43" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="43" t="n"/>
+      <c r="I19" s="43" t="n"/>
+      <c r="J19" s="43" t="n"/>
+      <c r="K19" s="43" t="n"/>
+      <c r="L19" s="43" t="n"/>
+      <c r="M19" s="43" t="n"/>
+      <c r="N19" s="43" t="n"/>
+      <c r="O19" s="43" t="n"/>
+      <c r="P19" s="43" t="n"/>
+      <c r="Q19" s="43" t="n"/>
+      <c r="R19" s="43" t="n"/>
+      <c r="S19" s="43" t="n"/>
+      <c r="T19" s="43" t="n"/>
+      <c r="U19" s="43" t="n"/>
+      <c r="V19" s="43" t="n"/>
+      <c r="W19" s="43" t="n"/>
+      <c r="X19" s="43" t="n"/>
+      <c r="Y19" s="43" t="n"/>
+      <c r="Z19" s="43" t="n"/>
+      <c r="AA19" s="43" t="n"/>
+      <c r="AB19" s="43" t="n"/>
+      <c r="AC19" s="43" t="n"/>
+      <c r="AD19" s="43" t="n"/>
+      <c r="AE19" s="43" t="n"/>
+      <c r="AF19" s="43" t="n"/>
+      <c r="AG19" s="43" t="n"/>
+      <c r="AH19" s="43" t="n"/>
+      <c r="AI19" s="43" t="n"/>
+      <c r="AJ19" s="43" t="n"/>
+      <c r="AK19" s="44" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -6839,13 +6939,13 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A5:AK5"/>
     <mergeCell ref="N3:Y3"/>
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="A10:AK10"/>
     <mergeCell ref="A13:AK13"/>
+    <mergeCell ref="A5:AK5"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="Z3:AK3"/>
   </mergeCells>
@@ -7511,4 +7611,690 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="45" t="inlineStr">
+        <is>
+          <t>UNLID SME市場単価調査——中小企業が払える金額・サービス別分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>調査時点：2024〜2026年  ／  対象：従業員30〜300名の日本国内中小企業（SME）  ／  単位：万円（月額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="47" t="inlineStr">
+        <is>
+          <t>① 業務アウトソーシング・支援サービス 市場相場（SME向け）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>業務カテゴリ</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>相場下限（万円/月）</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>相場上限（万円/月）</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>最多価格帯</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>UNLIDとの関係</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>主要データ出典</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>経理・バックオフィスBPO</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>月5〜10万</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>UNLID若手が補完する領域</t>
+        </is>
+      </c>
+      <c r="F6" s="50" t="inlineStr">
+        <is>
+          <t>キャスター社公開料金(2025)・フジ子さん公式サイト(2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>採用支援・HRコンサル</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>月15〜20万</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>UNLIDの競合＆補完領域</t>
+        </is>
+      </c>
+      <c r="F7" s="50" t="inlineStr">
+        <is>
+          <t>帝国データバンク「HR関連支出調査」2024年</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>IT・DX推進支援（週1顧問）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>月15〜20万</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>UNLIDの直接競合価格帯</t>
+        </is>
+      </c>
+      <c r="F8" s="50" t="inlineStr">
+        <is>
+          <t>中小企業庁「IT活用支援事業」公式資料2025年</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>マーケティング・SNS代行</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>月15〜25万</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>UNLIDクエストの一部として提供可</t>
+        </is>
+      </c>
+      <c r="F9" s="50" t="inlineStr">
+        <is>
+          <t>Web担当者Forum「外注マーケ費調査」2024年</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>外部CTO・技術顧問（週1〜2）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" s="49" t="inlineStr">
+        <is>
+          <t>月40〜60万</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>UNLIDより高単価の上位市場</t>
+        </is>
+      </c>
+      <c r="F10" s="50" t="inlineStr">
+        <is>
+          <t>サーキュレーション・顧問名鑑 公開料金(2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>DXコンサル（大手系）</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D11" s="49" t="inlineStr">
+        <is>
+          <t>月80〜120万</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>UNLIDより5〜10倍高い。SMEは手が出ない</t>
+        </is>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
+        <is>
+          <t>野村総研・アクセンチュア等提案書事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>AI導入支援（スポット）</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" s="49" t="inlineStr">
+        <is>
+          <t>プロジェクト型</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>UNLIDのプロジェクト型収益（3ヶ月80〜200万）</t>
+        </is>
+      </c>
+      <c r="F12" s="50" t="inlineStr">
+        <is>
+          <t>矢野経済研究所「AI導入コスト調査」2024年</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="51" t="inlineStr">
+        <is>
+          <t>★ UNLID フラクショナルFDE</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>月20〜30万</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>IT顧問より安く・ROI明確・最低単価20万円設定</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>本資料 競合分析＆SME支払意欲調査</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>② SMEが月20〜30万円を払うことへのROI根拠（業務別）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>SMEの業務課題（痛み）</t>
+        </is>
+      </c>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>UNLID対応クエスト</t>
+        </is>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>月額費用</t>
+        </is>
+      </c>
+      <c r="D16" s="48" t="inlineStr">
+        <is>
+          <t>期待ROI（月）</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="inlineStr">
+        <is>
+          <t>ROI根拠</t>
+        </is>
+      </c>
+      <c r="F16" s="48" t="inlineStr">
+        <is>
+          <t>データ出典</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>議事録・報告書・メール返信が多すぎて残業が止まらない</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>AI出力仕上げ・資料整理代行（ワーカー）</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>月5〜15万</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>月6〜10万の工数削減（30〜50h×時給2,000円）</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>残業削減＋担当者の高付加価値業務へのシフト</t>
+        </is>
+      </c>
+      <c r="F17" s="50" t="inlineStr">
+        <is>
+          <t>リクルートワークス「業務効率化調査」2024・パーソル総研「働き方調査」2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>採用が決まらない・採用媒体費が高い</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>採用ブランディング記事・求人票AI強化（ワーカー担当）</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>月10〜20万</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>採用媒体費50〜200万/年の削減効果</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>採用ミスマッチ損失（年収×3倍相当）の回避</t>
+        </is>
+      </c>
+      <c r="F18" s="50" t="inlineStr">
+        <is>
+          <t>エン・ジャパン「中小企業採用コスト調査」2025年。採用1人あたり平均43万円</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>AIを使えと言われるが何から始めていいかわからない</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>FDEが業務整理→AI1つ選定→3ヶ月で成果事例化</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="inlineStr">
+        <is>
+          <t>月20〜30万</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>DXコンサル（月50〜200万）の1/5〜1/10のコストで同等効果</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>IT投資対効果：中小企業白書2024（生産性20〜35%向上事例多数）</t>
+        </is>
+      </c>
+      <c r="F19" s="50" t="inlineStr">
+        <is>
+          <t>中小企業庁「2024年版中小企業白書」DX推進成功事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>問い合わせ対応に時間がかかりすぎる</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>FAQ整理・チャットボット設定補助・対応マニュアルAI化</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>月8〜15万</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>対応工数30〜50%削減。担当者の本業集中</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>1件あたり対応コスト2,500円×月200件×30%削減=月15万円相当</t>
+        </is>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
+        <is>
+          <t>矢野経済研究所「チャットボット市場」2024年。中小向け導入相場5〜30万/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>新入社員が育たない・先輩が育成に時間を割けない</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>新入社員ロープレ相手＋FBログ（ワーカーが対応）</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="inlineStr">
+        <is>
+          <t>月5〜15万</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>離職防止効果。離職コスト（年収×1.5〜3倍）の回避</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>OJT崩壊データ：計画的OJT実施率40.9%→30.3%に低下（2025年）</t>
+        </is>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
+        <is>
+          <t>パーソル総合研究所「OJTに関する定量調査」2025年1月</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="47" t="inlineStr">
+        <is>
+          <t>③ 価格帯別 SME継続率・解約率仮説（業界ベンチマーク比較）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>月額価格帯</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>想定継続月数</t>
+        </is>
+      </c>
+      <c r="C24" s="48" t="inlineStr">
+        <is>
+          <t>3ヶ月継続率</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>12ヶ月継続率</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>解約リスク要因</t>
+        </is>
+      </c>
+      <c r="F24" s="48" t="inlineStr">
+        <is>
+          <t>参考：類似SaaSベンチマーク</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>月5〜10万（格安BPO）</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>平均3〜6ヶ月</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="inlineStr">
+        <is>
+          <t>65〜75%</t>
+        </is>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>40〜55%</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>ROIが見えにくい・担当者変更</t>
+        </is>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>Lancers等クラウドBPO実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>月10〜20万（中間価格帯）</t>
+        </is>
+      </c>
+      <c r="B26" s="49" t="inlineStr">
+        <is>
+          <t>平均6〜12ヶ月</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>70〜80%</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>50〜65%</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>効果の可視化が鍵</t>
+        </is>
+      </c>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t>HRコンサル・IT顧問業界ベンチマーク</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="51" t="inlineStr">
+        <is>
+          <t>月20〜30万（★UNLID価格帯）</t>
+        </is>
+      </c>
+      <c r="B27" s="56" t="inlineStr">
+        <is>
+          <t>平均12〜18ヶ月</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>80〜88%</t>
+        </is>
+      </c>
+      <c r="D27" s="53" t="inlineStr">
+        <is>
+          <t>65〜75%</t>
+        </is>
+      </c>
+      <c r="E27" s="54" t="inlineStr">
+        <is>
+          <t>ROI可視化と完遂ログが継続を後押し</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>UNLIDベースライン仮説（3ヶ月でKPI達成設計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>月30〜60万（外部CTO相場）</t>
+        </is>
+      </c>
+      <c r="B28" s="49" t="inlineStr">
+        <is>
+          <t>平均12〜24ヶ月</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>80〜90%</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>65〜75%</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>担当者変更・予算削減</t>
+        </is>
+      </c>
+      <c r="F28" s="50" t="inlineStr">
+        <is>
+          <t>サーキュレーション顧客定着率実績（参考）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="57" t="inlineStr">
+        <is>
+          <t>【データ出典・注記】本シートのデータは公開資料・業界調査に基づく推計値（2024〜2026年）。詳細：中小企業庁「2024年版中小企業白書」/ 帝国データバンク各種産業調査 / パーソル総合研究所「OJT調査2025」/ リクルートワークス研究所 / 矢野経済研究所 / 各社公開料金表（キャスター・フジ子さん・サーキュレーション・顧問名鑑）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>